--- a/data/trans_dic/P16A07-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A07-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antidepresivos en las dos últimas semanas</t>
+          <t>Población que ha consumido antidepresivos en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,96</t>
+          <t>0,0; 0,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,58</t>
+          <t>0,18; 1,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,16</t>
+          <t>0,0; 1,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,77</t>
+          <t>0,0; 2,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,26</t>
+          <t>0,97; 3,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,92</t>
+          <t>0,23; 1,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,95</t>
+          <t>0,23; 1,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 5,97</t>
+          <t>0,71; 6,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,75</t>
+          <t>0,49; 1,77</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,42</t>
+          <t>0,23; 1,31</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,35</t>
+          <t>0,24; 1,34</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 3,07</t>
+          <t>0,38; 2,73</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,16</t>
+          <t>0,54; 2,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,99</t>
+          <t>0,82; 2,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,0</t>
+          <t>0,36; 2,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,04; 1,7</t>
+          <t>0,04; 1,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,82</t>
+          <t>1,83; 4,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 5,21</t>
+          <t>1,92; 5,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,57</t>
+          <t>1,19; 3,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,59</t>
+          <t>1,31; 4,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 3,01</t>
+          <t>1,39; 2,96</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,56; 3,37</t>
+          <t>1,56; 3,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,31</t>
+          <t>0,99; 2,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,0</t>
+          <t>0,97; 2,92</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,53</t>
+          <t>1,24; 3,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,99</t>
+          <t>1,86; 4,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,44</t>
+          <t>1,14; 3,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,34</t>
+          <t>1,48; 4,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,47; 5,56</t>
+          <t>2,44; 5,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,06; 10,26</t>
+          <t>6,04; 10,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,88; 5,82</t>
+          <t>2,98; 6,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 6,06</t>
+          <t>3,21; 6,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,12; 4,01</t>
+          <t>2,16; 4,02</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,4; 7,05</t>
+          <t>4,45; 6,99</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,31; 4,16</t>
+          <t>2,31; 4,13</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,62; 4,75</t>
+          <t>2,67; 4,84</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,9</t>
+          <t>1,16; 4,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 5,49</t>
+          <t>2,1; 5,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,12</t>
+          <t>1,42; 3,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 6,33</t>
+          <t>1,49; 6,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,64; 11,48</t>
+          <t>6,5; 11,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,26; 11,96</t>
+          <t>7,12; 11,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,53; 11,15</t>
+          <t>6,48; 11,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,27; 9,79</t>
+          <t>6,22; 9,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,23; 7,09</t>
+          <t>4,21; 7,06</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,94; 7,8</t>
+          <t>5,1; 7,92</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,36; 6,92</t>
+          <t>4,34; 7,12</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,28; 7,27</t>
+          <t>3,59; 7,33</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,13; 5,58</t>
+          <t>2,18; 5,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,67; 8,44</t>
+          <t>3,76; 8,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,41; 6,31</t>
+          <t>2,46; 6,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,15; 8,28</t>
+          <t>4,22; 8,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,58; 16,26</t>
+          <t>9,48; 16,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,53; 19,55</t>
+          <t>12,42; 19,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,67; 14,31</t>
+          <t>8,53; 14,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,56; 14,83</t>
+          <t>10,67; 15,01</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,44; 10,22</t>
+          <t>6,42; 10,2</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,87; 13,29</t>
+          <t>8,91; 13,15</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,03; 9,54</t>
+          <t>6,05; 9,55</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,93; 10,72</t>
+          <t>7,89; 10,85</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,16; 6,72</t>
+          <t>2,11; 6,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,34; 7,38</t>
+          <t>2,29; 7,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,86; 4,02</t>
+          <t>0,84; 3,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,92</t>
+          <t>1,33; 4,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,33; 13,57</t>
+          <t>7,38; 13,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,41; 16,8</t>
+          <t>9,93; 17,1</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,43; 17,8</t>
+          <t>10,07; 17,12</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,16; 12,81</t>
+          <t>3,17; 12,69</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,33; 9,38</t>
+          <t>5,55; 9,34</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,97; 11,24</t>
+          <t>6,99; 11,34</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6,25; 10,62</t>
+          <t>5,99; 10,32</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,04; 8,03</t>
+          <t>2,98; 7,92</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,51; 8,51</t>
+          <t>2,34; 8,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,05; 9,74</t>
+          <t>3,03; 9,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,24; 6,9</t>
+          <t>2,3; 6,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,17; 8,83</t>
+          <t>4,34; 8,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,63; 13,55</t>
+          <t>6,73; 13,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,49; 15,36</t>
+          <t>8,48; 15,32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,49; 15,77</t>
+          <t>8,15; 15,59</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,17; 12,39</t>
+          <t>8,19; 12,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,59; 10,4</t>
+          <t>5,67; 10,47</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6,99; 11,58</t>
+          <t>6,67; 11,62</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,69; 11,24</t>
+          <t>6,64; 11,47</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,08; 10,13</t>
+          <t>7,05; 10,08</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,62</t>
+          <t>1,68; 2,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,53; 3,91</t>
+          <t>2,53; 3,89</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,7; 2,69</t>
+          <t>1,73; 2,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,45; 3,92</t>
+          <t>2,47; 3,88</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,63; 7,3</t>
+          <t>5,65; 7,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,41; 9,26</t>
+          <t>7,46; 9,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,29; 8,0</t>
+          <t>6,23; 8,14</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,76; 7,97</t>
+          <t>5,85; 8,03</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,84; 4,81</t>
+          <t>3,89; 4,8</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5,28; 6,44</t>
+          <t>5,23; 6,44</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,19; 5,23</t>
+          <t>4,24; 5,27</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,53; 5,82</t>
+          <t>4,55; 5,8</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antidepresivos en las dos últimas semanas</t>
+          <t>Población que ha consumido antidepresivos en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4750</t>
+          <t>0; 4843</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>800; 7142</t>
+          <t>817; 8098</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 9058</t>
+          <t>0; 6977</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 7084</t>
+          <t>0; 8806</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3930; 15220</t>
+          <t>4549; 15954</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>979; 8209</t>
+          <t>974; 8130</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>924; 7726</t>
+          <t>921; 7747</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2200; 18695</t>
+          <t>2213; 19671</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4663; 16829</t>
+          <t>4696; 17056</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2243; 12504</t>
+          <t>1990; 11541</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1899; 10970</t>
+          <t>1953; 10914</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3420; 21866</t>
+          <t>2704; 19439</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4065; 15865</t>
+          <t>3998; 16097</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5004; 20492</t>
+          <t>5648; 20514</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1972; 11838</t>
+          <t>2112; 12777</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>164; 7186</t>
+          <t>166; 7917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12038; 30173</t>
+          <t>11454; 30178</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11684; 31722</t>
+          <t>11667; 30667</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6641; 20139</t>
+          <t>6723; 21198</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6189; 23469</t>
+          <t>6676; 23922</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19018; 41014</t>
+          <t>18956; 40270</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20238; 43718</t>
+          <t>20148; 43582</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10412; 26644</t>
+          <t>11410; 27196</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9158; 28096</t>
+          <t>9067; 27339</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7517; 22521</t>
+          <t>7912; 23648</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12982; 33916</t>
+          <t>12656; 33961</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7676; 23007</t>
+          <t>7644; 23439</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7661; 23300</t>
+          <t>7956; 24636</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>17071; 38338</t>
+          <t>16834; 36937</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>42890; 72600</t>
+          <t>42730; 72647</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19063; 38496</t>
+          <t>19737; 40516</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17992; 32894</t>
+          <t>17400; 32531</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>28203; 53269</t>
+          <t>28700; 53312</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>61039; 97894</t>
+          <t>61708; 97011</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30671; 55368</t>
+          <t>30759; 54923</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>28262; 51213</t>
+          <t>28752; 52204</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6057; 20229</t>
+          <t>6033; 21137</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12456; 33762</t>
+          <t>12935; 32740</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9366; 26646</t>
+          <t>9169; 24376</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15211; 56184</t>
+          <t>13254; 54075</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>34231; 59200</t>
+          <t>33510; 60117</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>44581; 73436</t>
+          <t>43726; 71760</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>42357; 72393</t>
+          <t>42046; 71685</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>44669; 69784</t>
+          <t>44339; 68760</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>43766; 73417</t>
+          <t>43595; 73104</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>60680; 95855</t>
+          <t>62721; 97290</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>56453; 89570</t>
+          <t>56217; 92234</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>52547; 116351</t>
+          <t>57447; 117366</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8237; 21577</t>
+          <t>8442; 22481</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15663; 36044</t>
+          <t>16060; 37005</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11518; 30152</t>
+          <t>11752; 30992</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23247; 46383</t>
+          <t>23639; 45124</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>38718; 65704</t>
+          <t>38310; 65623</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>56105; 87543</t>
+          <t>55633; 86537</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>43092; 71079</t>
+          <t>42371; 71836</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>57524; 80821</t>
+          <t>58142; 81772</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>50909; 80847</t>
+          <t>50759; 80642</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>77580; 116304</t>
+          <t>77941; 115074</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>58809; 93007</t>
+          <t>58969; 93059</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>87618; 118457</t>
+          <t>87173; 119936</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6311; 19659</t>
+          <t>6170; 19291</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7202; 22700</t>
+          <t>7058; 23291</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2892; 13440</t>
+          <t>2807; 12590</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5048; 14449</t>
+          <t>4883; 14766</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>25121; 46552</t>
+          <t>25322; 46639</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33315; 59457</t>
+          <t>35144; 60539</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>39406; 67226</t>
+          <t>38055; 64677</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>19202; 77952</t>
+          <t>19311; 77228</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>33846; 59622</t>
+          <t>35277; 59367</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>46152; 74412</t>
+          <t>46292; 75069</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>44478; 75603</t>
+          <t>42666; 73513</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>29658; 78388</t>
+          <t>29082; 77377</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5260; 17868</t>
+          <t>4919; 17812</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7608; 24260</t>
+          <t>7549; 23963</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5751; 17733</t>
+          <t>5915; 17071</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11774; 24938</t>
+          <t>12250; 24792</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>22145; 45229</t>
+          <t>22483; 44457</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>32731; 59224</t>
+          <t>32709; 59077</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33983; 63094</t>
+          <t>32631; 62401</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>34681; 52575</t>
+          <t>34739; 52070</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>30386; 56535</t>
+          <t>30817; 56944</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>44342; 73517</t>
+          <t>42334; 73746</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>43941; 73856</t>
+          <t>43633; 75394</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>50024; 71581</t>
+          <t>49787; 71202</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>55089; 85755</t>
+          <t>55132; 88484</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>86572; 133555</t>
+          <t>86537; 132995</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>57849; 91412</t>
+          <t>58629; 92928</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>84745; 135474</t>
+          <t>85505; 134337</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>190280; 246748</t>
+          <t>190996; 247695</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>262752; 328478</t>
+          <t>264554; 331394</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>223043; 283410</t>
+          <t>220920; 288598</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>210501; 291456</t>
+          <t>214142; 293572</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>255230; 320257</t>
+          <t>259067; 319516</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>367529; 448340</t>
+          <t>364473; 448511</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>290464; 362774</t>
+          <t>294186; 365908</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>322144; 414280</t>
+          <t>323773; 413007</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A07-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A07-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -717,27 +717,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,98</t>
+          <t>0,0; 1,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,79</t>
+          <t>0,18; 1,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,66</t>
+          <t>0,0; 1,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,2</t>
+          <t>0,0; 2,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,41</t>
+          <t>0,84; 3,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -747,32 +747,32 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,96</t>
+          <t>0,23; 1,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 6,28</t>
+          <t>0,61; 5,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,77</t>
+          <t>0,49; 1,87</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,31</t>
+          <t>0,22; 1,39</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,34</t>
+          <t>0,23; 1,34</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,73</t>
+          <t>0,56; 2,93</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -857,42 +857,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,19</t>
+          <t>0,59; 2,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,99</t>
+          <t>0,7; 2,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,16</t>
+          <t>0,48; 2,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,04; 1,87</t>
+          <t>0,25; 2,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,82</t>
+          <t>1,94; 4,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 5,03</t>
+          <t>1,83; 4,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,76</t>
+          <t>1,18; 3,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,68</t>
+          <t>1,53; 4,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,56; 3,36</t>
+          <t>1,54; 3,34</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,36</t>
+          <t>0,92; 2,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,92</t>
+          <t>1,12; 2,96</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,71</t>
+          <t>1,2; 3,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,99</t>
+          <t>1,95; 5,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,5</t>
+          <t>1,25; 3,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,59</t>
+          <t>1,31; 4,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,44; 5,36</t>
+          <t>2,37; 5,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,04; 10,27</t>
+          <t>6,03; 10,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,98; 6,13</t>
+          <t>2,94; 5,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,0</t>
+          <t>3,13; 5,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,16; 4,02</t>
+          <t>2,1; 4,04</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,45; 6,99</t>
+          <t>4,33; 7,01</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,31; 4,13</t>
+          <t>2,34; 4,22</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,67; 4,84</t>
+          <t>2,53; 4,48</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,07</t>
+          <t>1,13; 3,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 5,33</t>
+          <t>2,05; 5,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,77</t>
+          <t>1,52; 3,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 6,09</t>
+          <t>3,82; 7,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,5; 11,66</t>
+          <t>6,74; 11,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,12; 11,69</t>
+          <t>7,2; 11,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,48; 11,04</t>
+          <t>6,41; 10,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,22; 9,65</t>
+          <t>6,9; 10,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,21; 7,06</t>
+          <t>4,3; 7,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,1; 7,92</t>
+          <t>5,07; 7,82</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,34; 7,12</t>
+          <t>4,33; 6,88</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,59; 7,33</t>
+          <t>5,8; 8,13</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,12%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 5,81</t>
+          <t>2,11; 5,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,76; 8,66</t>
+          <t>3,86; 8,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,46; 6,48</t>
+          <t>2,31; 6,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,22; 8,05</t>
+          <t>4,04; 7,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,48; 16,24</t>
+          <t>9,42; 16,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,42; 19,32</t>
+          <t>12,8; 19,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,53; 14,46</t>
+          <t>8,59; 14,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,67; 15,01</t>
+          <t>10,68; 14,94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,42; 10,2</t>
+          <t>6,4; 10,25</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,91; 13,15</t>
+          <t>8,94; 13,31</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,05; 9,55</t>
+          <t>5,96; 9,47</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,89; 10,85</t>
+          <t>7,8; 10,64</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,11; 6,59</t>
+          <t>1,97; 6,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,29; 7,57</t>
+          <t>2,33; 7,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,77</t>
+          <t>0,86; 4,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,33; 4,01</t>
+          <t>1,26; 3,95</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,38; 13,6</t>
+          <t>7,33; 13,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,93; 17,1</t>
+          <t>9,72; 16,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,07; 17,12</t>
+          <t>10,34; 17,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,17; 12,69</t>
+          <t>9,84; 14,42</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5,55; 9,34</t>
+          <t>5,37; 9,26</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6,99; 11,34</t>
+          <t>6,98; 11,48</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5,99; 10,32</t>
+          <t>6,11; 10,32</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,98; 7,92</t>
+          <t>6,02; 8,77</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,34; 8,49</t>
+          <t>2,51; 8,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,03; 9,62</t>
+          <t>2,99; 9,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,3; 6,64</t>
+          <t>2,13; 6,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,34; 8,78</t>
+          <t>4,03; 8,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,73; 13,31</t>
+          <t>6,9; 13,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,48; 15,32</t>
+          <t>8,35; 15,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,15; 15,59</t>
+          <t>8,66; 15,89</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,19; 12,27</t>
+          <t>8,1; 12,3</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,67; 10,47</t>
+          <t>5,72; 10,76</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6,67; 11,62</t>
+          <t>6,86; 11,57</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,64; 11,47</t>
+          <t>6,64; 11,29</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,05; 10,08</t>
+          <t>6,88; 10,13</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,7</t>
+          <t>1,68; 2,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,53; 3,89</t>
+          <t>2,52; 3,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,73; 2,74</t>
+          <t>1,72; 2,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,47; 3,88</t>
+          <t>2,85; 4,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,65; 7,33</t>
+          <t>5,64; 7,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,46; 9,34</t>
+          <t>7,41; 9,44</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,23; 8,14</t>
+          <t>6,29; 8,08</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,85; 8,03</t>
+          <t>6,95; 8,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3,89; 4,8</t>
+          <t>3,86; 4,86</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5,23; 6,44</t>
+          <t>5,21; 6,38</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,24; 5,27</t>
+          <t>4,25; 5,28</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,55; 5,8</t>
+          <t>5,17; 6,12</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>2961</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7229</t>
+          <t>7804</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8732</t>
+          <t>10765</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4843</t>
+          <t>0; 5797</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>817; 8098</t>
+          <t>810; 7735</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6977</t>
+          <t>0; 7648</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 8806</t>
+          <t>0; 10029</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4549; 15954</t>
+          <t>3913; 15957</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>974; 8130</t>
+          <t>978; 8130</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>921; 7747</t>
+          <t>925; 7715</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2213; 19671</t>
+          <t>2197; 18356</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4696; 17056</t>
+          <t>4679; 17982</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1990; 11541</t>
+          <t>1983; 12276</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1953; 10914</t>
+          <t>1907; 10951</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2704; 19439</t>
+          <t>4296; 22570</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2287</t>
+          <t>4051</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13787</t>
+          <t>13846</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16074</t>
+          <t>17897</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3998; 16097</t>
+          <t>4363; 15941</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5648; 20514</t>
+          <t>4827; 19645</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2112; 12777</t>
+          <t>2858; 12016</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>166; 7917</t>
+          <t>1176; 10978</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11454; 30178</t>
+          <t>12127; 30771</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11667; 30667</t>
+          <t>11150; 29713</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6723; 21198</t>
+          <t>6627; 19456</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6676; 23922</t>
+          <t>7673; 24759</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18956; 40270</t>
+          <t>18956; 40255</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20148; 43582</t>
+          <t>19977; 43259</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11410; 27196</t>
+          <t>10573; 27240</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9067; 27339</t>
+          <t>10991; 28957</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14218</t>
+          <t>14662</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24693</t>
+          <t>27638</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>38911</t>
+          <t>42300</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7912; 23648</t>
+          <t>7682; 23315</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12656; 33961</t>
+          <t>13295; 35272</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7644; 23439</t>
+          <t>8337; 22502</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7956; 24636</t>
+          <t>8112; 26523</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>16834; 36937</t>
+          <t>16377; 36220</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>42730; 72647</t>
+          <t>42640; 73317</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19737; 40516</t>
+          <t>19470; 39410</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17400; 32531</t>
+          <t>19477; 36830</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>28700; 53312</t>
+          <t>27891; 53628</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>61708; 97011</t>
+          <t>60143; 97300</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30759; 54923</t>
+          <t>31141; 56101</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>28752; 52204</t>
+          <t>31489; 55660</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34881</t>
+          <t>37388</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>56444</t>
+          <t>61485</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91324</t>
+          <t>98873</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6033; 21137</t>
+          <t>5877; 19962</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12935; 32740</t>
+          <t>12626; 32964</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9169; 24376</t>
+          <t>9794; 25343</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13254; 54075</t>
+          <t>26764; 52955</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>33510; 60117</t>
+          <t>34729; 59469</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>43726; 71760</t>
+          <t>44210; 71770</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>42046; 71685</t>
+          <t>41604; 70692</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>44339; 68760</t>
+          <t>50857; 73770</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>43595; 73104</t>
+          <t>44493; 73853</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>62721; 97290</t>
+          <t>62316; 96075</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>56217; 92234</t>
+          <t>56097; 89118</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>57447; 117366</t>
+          <t>83427; 116909</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32795</t>
+          <t>34295</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>69072</t>
+          <t>76553</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>101867</t>
+          <t>110848</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8442; 22481</t>
+          <t>8163; 23121</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>16060; 37005</t>
+          <t>16482; 36929</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11752; 30992</t>
+          <t>11048; 30006</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23639; 45124</t>
+          <t>24593; 45973</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>38310; 65623</t>
+          <t>38058; 64865</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>55633; 86537</t>
+          <t>57307; 88028</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>42371; 71836</t>
+          <t>42668; 70766</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>58142; 81772</t>
+          <t>64882; 90726</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>50759; 80642</t>
+          <t>50602; 81082</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>77941; 115074</t>
+          <t>78263; 116507</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>58969; 93059</t>
+          <t>58088; 92291</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>87173; 119936</t>
+          <t>94801; 129304</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8778</t>
+          <t>9554</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>48197</t>
+          <t>52275</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>56975</t>
+          <t>61830</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6170; 19291</t>
+          <t>5757; 18803</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7058; 23291</t>
+          <t>7164; 22991</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2807; 12590</t>
+          <t>2883; 14516</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4883; 14766</t>
+          <t>5132; 16065</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>25322; 46639</t>
+          <t>25152; 46830</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>35144; 60539</t>
+          <t>34398; 58880</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38055; 64677</t>
+          <t>39056; 66311</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>19311; 77228</t>
+          <t>43198; 63321</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>35277; 59367</t>
+          <t>34156; 58844</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>46292; 75069</t>
+          <t>46217; 76002</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>42666; 73513</t>
+          <t>43531; 73477</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>29082; 77377</t>
+          <t>50938; 74257</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17294</t>
+          <t>18843</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>42775</t>
+          <t>46656</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>60069</t>
+          <t>65498</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4919; 17812</t>
+          <t>5261; 18074</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>7549; 23963</t>
+          <t>7449; 23488</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5915; 17071</t>
+          <t>5483; 16938</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12250; 24792</t>
+          <t>12469; 26343</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>22483; 44457</t>
+          <t>23048; 46258</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>32709; 59077</t>
+          <t>32192; 57881</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32631; 62401</t>
+          <t>34670; 63600</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>34739; 52070</t>
+          <t>37525; 56972</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>30817; 56944</t>
+          <t>31091; 58518</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>42334; 73746</t>
+          <t>43528; 73448</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>43633; 75394</t>
+          <t>43640; 74189</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>49787; 71202</t>
+          <t>53189; 78291</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>111757</t>
+          <t>121754</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>262196</t>
+          <t>286257</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>373953</t>
+          <t>408011</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>55132; 88484</t>
+          <t>54910; 87621</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>86537; 132995</t>
+          <t>86262; 133819</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>58629; 92928</t>
+          <t>58476; 94031</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>85505; 134337</t>
+          <t>100742; 146123</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>190996; 247695</t>
+          <t>190667; 247809</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>264554; 331394</t>
+          <t>262954; 334706</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>220920; 288598</t>
+          <t>223117; 286399</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>214142; 293572</t>
+          <t>259442; 312595</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>259067; 319516</t>
+          <t>256746; 323336</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>364473; 448511</t>
+          <t>362663; 444459</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>294186; 365908</t>
+          <t>294586; 366535</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>323773; 413007</t>
+          <t>375286; 444858</t>
         </is>
       </c>
     </row>
